--- a/data/household/excel-web.xlsx
+++ b/data/household/excel-web.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Jumlah Gerai</t>
+          <t>Jumlah GraPARI</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
